--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -507,25 +507,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>50</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>50</v>
+        <v>3.57</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -554,13 +554,13 @@
         <v>15.79</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -839,22 +839,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>92.86</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>7.14</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -871,22 +874,25 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>15.79</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.4</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -967,22 +973,25 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -999,22 +1008,25 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1031,22 +1043,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>32.14</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1063,22 +1078,25 @@
         <v>19</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
   </sheetData>
@@ -1147,25 +1165,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>50</v>
+        <v>92.86</v>
       </c>
       <c r="H2" s="1">
-        <v>50</v>
+        <v>7.14</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1194,13 +1212,13 @@
         <v>15.79</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1299,7 +1317,7 @@
         <v>3.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1322,19 +1340,19 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -1369,7 +1387,7 @@
         <v>32.14</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1404,7 +1422,7 @@
         <v>5.26</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>1</v>

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -886,13 +886,13 @@
         <v>15.79</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -909,22 +909,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -941,22 +944,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.1</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1235,16 +1241,16 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I4" s="2">
         <v>8.6</v>
@@ -1270,19 +1276,19 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>90.48</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>9.52</v>
+        <v>14.29</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -659,13 +659,13 @@
         <v>3.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -694,13 +694,13 @@
         <v>23.81</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -994,10 +994,10 @@
         <v>7.7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1014,25 +1014,25 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1323,13 +1323,13 @@
         <v>3.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1346,25 +1346,25 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -717,25 +717,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>32.14</v>
+        <v>3.57</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -764,13 +764,13 @@
         <v>5.26</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1049,25 +1049,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>32.14</v>
+        <v>3.57</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1096,13 +1096,13 @@
         <v>5.26</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1381,25 +1381,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>32.14</v>
+        <v>3.57</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1428,13 +1428,13 @@
         <v>5.26</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -1241,19 +1241,19 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1276,16 +1276,16 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="I5" s="2">
         <v>7.9</v>
@@ -1311,19 +1311,19 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>4.76</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -1183,7 +1183,7 @@
         <v>7.14</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1206,19 +1206,19 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H3" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>4.76</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20221.xlsx
+++ b/academias/Programación - Estadisticos 20221.xlsx
@@ -1381,19 +1381,19 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H8" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1416,19 +1416,19 @@
         <v>19</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H9" s="1">
-        <v>5.26</v>
+        <v>10.53</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
